--- a/Result/profitability/4956.xlsx
+++ b/Result/profitability/4956.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.41</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.13375</v>
+        <v>-0.12875</v>
       </c>
       <c r="N2" t="n">
-        <v>8.69</v>
+        <v>8.735000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.99</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.009999999999999995</v>
+        <v>0.007499999999999993</v>
       </c>
       <c r="N3" t="n">
-        <v>11.2325</v>
+        <v>11.885</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06000000000000001</v>
+        <v>0.0925</v>
       </c>
       <c r="N4" t="n">
-        <v>14.07875</v>
+        <v>15.34625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.18875</v>
+        <v>0.29</v>
       </c>
       <c r="N5" t="n">
-        <v>17.985</v>
+        <v>19.9075</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="N6" t="n">
-        <v>23.435</v>
+        <v>24.8675</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>0.50375</v>
+        <v>0.48</v>
       </c>
       <c r="N7" t="n">
-        <v>28.46125</v>
+        <v>28.56125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -9068,6 +9068,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4956</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>363</v>
+      </c>
+      <c r="D69" t="n">
+        <v>310</v>
+      </c>
+      <c r="E69" t="n">
+        <v>53</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>4</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-0.0775</v>
+      </c>
+      <c r="N69" t="n">
+        <v>9.94125</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>-5.449999999999999</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.2707401887729757</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-1.051948051948052</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-21.97142857142857</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
